--- a/document/ログイン機能_詳細クラス図.xlsx
+++ b/document/ログイン機能_詳細クラス図.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER122\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DAA8E154-C0C3-47AA-B07B-002889B45B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D5F0A3-E7C5-40E2-98C5-3AA8141EEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
   </bookViews>
   <sheets>
     <sheet name="詳細クラス図（ログイン機能）" sheetId="1" r:id="rId1"/>
@@ -423,6 +423,45 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -432,82 +471,43 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="56" fontId="3" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -533,15 +533,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
+      <xdr:colOff>38100</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:rowOff>101600</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>1054100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -571,8 +571,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="990600" y="1457325"/>
-          <a:ext cx="9629775" cy="7800975"/>
+          <a:off x="1003300" y="1511300"/>
+          <a:ext cx="9645650" cy="7912100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -591,7 +591,109 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>984250</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="吹き出し: 角を丸めた四角形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FA66502B-C211-AA0A-9A05-9F714C4FF113}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2978150" y="7562850"/>
+          <a:ext cx="2774950" cy="730250"/>
+        </a:xfrm>
+        <a:prstGeom prst="wedgeRoundRectCallout">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -25862"/>
+            <a:gd name="adj2" fmla="val -69643"/>
+            <a:gd name="adj3" fmla="val 16667"/>
+          </a:avLst>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent4"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="lt1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent4"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
+            <a:t>レコード取得が</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
+            <a:t>成功→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
+            <a:t>UserBean</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
+            <a:t>がリターン</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
+            <a:t>失敗→</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
+            <a:t>null</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1000"/>
+            <a:t>がリターン</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -804,120 +906,120 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:13" ht="18" customHeight="1">
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="3"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="5" t="s">
+      <c r="C1" s="16"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="5" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="6"/>
-      <c r="I1" s="7" t="s">
+      <c r="H1" s="25"/>
+      <c r="I1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="4" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="2:13" ht="18" customHeight="1">
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="13" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="14"/>
-      <c r="G2" s="13" t="s">
+      <c r="F2" s="27"/>
+      <c r="G2" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="14"/>
-      <c r="I2" s="15">
+      <c r="H2" s="27"/>
+      <c r="I2" s="30">
         <v>46175</v>
       </c>
-      <c r="J2" s="16" t="s">
+      <c r="J2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="17"/>
+      <c r="K2" s="11"/>
     </row>
     <row r="3" spans="2:13" ht="18" customHeight="1">
-      <c r="B3" s="10"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="20"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="12"/>
     </row>
     <row r="4" spans="2:13" ht="18" customHeight="1" thickBot="1">
       <c r="B4" s="21"/>
       <c r="C4" s="22"/>
       <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="23"/>
-      <c r="G4" s="24"/>
+      <c r="G4" s="29"/>
       <c r="H4" s="23"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="26"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="13"/>
     </row>
     <row r="5" spans="2:13" ht="12.75" customHeight="1">
-      <c r="B5" s="27"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="29"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="7"/>
     </row>
     <row r="6" spans="2:13" ht="12.75" customHeight="1">
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="30" t="s">
+      <c r="C6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="30" t="s">
+      <c r="D6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="30" t="s">
+      <c r="F6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="G6" s="30" t="s">
+      <c r="G6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="30" t="s">
+      <c r="H6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="I6" s="30" t="s">
+      <c r="I6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="J6" s="30" t="s">
+      <c r="J6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="K6" s="30" t="s">
+      <c r="K6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="L6" s="30" t="s">
+      <c r="L6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="M6" s="30" t="s">
+      <c r="M6" s="14" t="s">
         <v>9</v>
       </c>
     </row>

--- a/document/ログイン機能_詳細クラス図.xlsx
+++ b/document/ログイン機能_詳細クラス図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D5F0A3-E7C5-40E2-98C5-3AA8141EEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC2A2D7-66BD-43BA-80F9-CED630A63E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
   </bookViews>
   <sheets>
     <sheet name="詳細クラス図（ログイン機能）" sheetId="1" r:id="rId1"/>
@@ -530,67 +530,6 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>1054100</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F61B37-9164-4C83-8201-A2D5EEE42BF8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1003300" y="1511300"/>
-          <a:ext cx="9645650" cy="7912100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -689,11 +628,57 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>353785</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>151313</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2607816-D845-246B-BC51-61F7308C96B5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="353785" y="1510393"/>
+          <a:ext cx="12833171" cy="10531928"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/document/ログイン機能_詳細クラス図.xlsx
+++ b/document/ログイン機能_詳細クラス図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BC2A2D7-66BD-43BA-80F9-CED630A63E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D5F0A3-E7C5-40E2-98C5-3AA8141EEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
+    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
   </bookViews>
   <sheets>
     <sheet name="詳細クラス図（ログイン機能）" sheetId="1" r:id="rId1"/>
@@ -530,6 +530,67 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>101600</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>1054100</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F61B37-9164-4C83-8201-A2D5EEE42BF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="1003300" y="1511300"/>
+          <a:ext cx="9645650" cy="7912100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
@@ -628,57 +689,11 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>353785</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>151313</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2607816-D845-246B-BC51-61F7308C96B5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="353785" y="1510393"/>
-          <a:ext cx="12833171" cy="10531928"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>

--- a/document/ログイン機能_詳細クラス図.xlsx
+++ b/document/ログイン機能_詳細クラス図.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\TaskMan\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D5F0A3-E7C5-40E2-98C5-3AA8141EEF48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C603DEA-6DFB-4852-B0D5-7A634CDEC242}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D661EF23-4996-4F1B-A97B-972546707383}"/>
   </bookViews>
   <sheets>
     <sheet name="詳細クラス図（ログイン機能）" sheetId="1" r:id="rId1"/>
@@ -533,15 +533,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:colOff>60512</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>748</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>1054100</xdr:colOff>
+      <xdr:colOff>1076512</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:rowOff>62380</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -571,8 +571,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="1003300" y="1511300"/>
-          <a:ext cx="9645650" cy="7912100"/>
+          <a:off x="1024218" y="1524748"/>
+          <a:ext cx="9610912" cy="7625603"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -689,11 +689,390 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>914400</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1200150</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56A152D4-F0DF-A9BD-A832-585CBE2E157F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2905125" y="4867275"/>
+          <a:ext cx="285750" cy="590550"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>324992</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>111756</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>325352</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>112116</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="5" name="インク 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E544178C-5DC7-30D0-C84E-7A39E2B5AF78}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="5446080" y="1792638"/>
+            <a:ext cx="360" cy="360"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="5" name="インク 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E544178C-5DC7-30D0-C84E-7A39E2B5AF78}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5439960" y="1786518"/>
+              <a:ext cx="12600" cy="12600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>336176</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>302559</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>336176</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="12" name="直線矢印コネクタ 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0606399D-5930-8C7A-2275-0829C9F75B0C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4347882" y="2297206"/>
+          <a:ext cx="0" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>974912</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>89647</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>151280</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>37540</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="正方形/長方形 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CECC364-DF7B-4929-9936-9BC1674CFCB2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8314765" y="7317441"/>
+          <a:ext cx="285750" cy="575423"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>39594</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>144182</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>39594</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>155388</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="直線矢印コネクタ 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33E65E7C-1585-462F-8080-A018F54C92A7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1003300" y="1511300"/>
+          <a:ext cx="0" cy="3048000"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>997323</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>1143000</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>44823</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>67236</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="17" name="直線矢印コネクタ 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{711121CD-BB3A-46FC-BC78-858F44D8C3BF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5009029" y="7115735"/>
+          <a:ext cx="1266265" cy="1120589"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+<file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2026-06-09T08:52:17.481"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">0 0 24575,'0'0'-8191</inkml:trace>
+</inkml:ink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
